--- a/backend/static_assets/SPOT_vs_iQuote_Round2.xlsx
+++ b/backend/static_assets/SPOT_vs_iQuote_Round2.xlsx
@@ -1504,7 +1504,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Avg Variance % — Top 15 Customers</a:t>
+              <a:t>Median Variance % — Top 15 Customers</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -1856,7 +1856,7 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>4</col>
+      <col>7</col>
       <colOff>0</colOff>
       <row>21</row>
       <rowOff>0</rowOff>
@@ -2858,7 +2858,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-09-01 10:50  |  Quote-total rows: 172  |  Unique estimates: 110</t>
+          <t>Generated 2026-09-01 12:26  |  Quote-total rows: 172  |  Unique estimates: 110</t>
         </is>
       </c>
     </row>
@@ -20843,7 +20843,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Avg Variance % — Top 15 Customers × Qty Band (Quote-Total Level)</t>
+          <t>Median Variance % — Top 15 Customers × Qty Band (Quote-Total Level)</t>
         </is>
       </c>
     </row>
@@ -20891,16 +20891,16 @@
         </is>
       </c>
       <c r="B4" s="17" t="n">
-        <v>35.90653605565359</v>
+        <v>34.2748707527717</v>
       </c>
       <c r="C4" s="17" t="n">
-        <v>-13.45422907107912</v>
+        <v>-19.1747177115131</v>
       </c>
       <c r="D4" s="17" t="n">
-        <v>15.17307220042718</v>
+        <v>23.54270046211048</v>
       </c>
       <c r="E4" s="17" t="n">
-        <v>8.827360078840293</v>
+        <v>9.134866938558464</v>
       </c>
       <c r="F4" s="17" t="n"/>
       <c r="G4" s="14" t="n">
@@ -20920,10 +20920,10 @@
         <v>2.960367327211211</v>
       </c>
       <c r="D5" s="17" t="n">
-        <v>16.21273643451724</v>
+        <v>21.53709052520965</v>
       </c>
       <c r="E5" s="17" t="n">
-        <v>-9.268851812370757</v>
+        <v>-22.58781548930945</v>
       </c>
       <c r="F5" s="17" t="n"/>
       <c r="G5" s="14" t="n">
@@ -20938,10 +20938,10 @@
       </c>
       <c r="B6" s="17" t="n"/>
       <c r="C6" s="17" t="n">
-        <v>39.26495297605675</v>
+        <v>34.13220472312226</v>
       </c>
       <c r="D6" s="17" t="n">
-        <v>35.34249013428767</v>
+        <v>31.81931826577036</v>
       </c>
       <c r="E6" s="17" t="n">
         <v>27.91070584328644</v>
@@ -20962,10 +20962,10 @@
         <v>3.753494963422579</v>
       </c>
       <c r="D7" s="17" t="n">
-        <v>23.96737655953212</v>
+        <v>23.81321432992468</v>
       </c>
       <c r="E7" s="17" t="n">
-        <v>13.79005223995886</v>
+        <v>14.04360567153324</v>
       </c>
       <c r="F7" s="17" t="n">
         <v>65.57995076887907</v>
@@ -20984,10 +20984,10 @@
         <v>56.92758476349936</v>
       </c>
       <c r="C8" s="17" t="n">
-        <v>29.30130994668932</v>
+        <v>32.16937561641097</v>
       </c>
       <c r="D8" s="17" t="n">
-        <v>18.06115108087893</v>
+        <v>16.87258286396553</v>
       </c>
       <c r="E8" s="17" t="n">
         <v>8.108483683442572</v>
@@ -21007,7 +21007,7 @@
         <v>-10.77085781433607</v>
       </c>
       <c r="C9" s="17" t="n">
-        <v>27.45532640314835</v>
+        <v>-0.9085616063994744</v>
       </c>
       <c r="D9" s="17" t="n">
         <v>27.35576923076924</v>
@@ -21031,7 +21031,7 @@
         <v>27.8076979100926</v>
       </c>
       <c r="D10" s="17" t="n">
-        <v>54.53371229848384</v>
+        <v>62.80048959608324</v>
       </c>
       <c r="E10" s="17" t="n">
         <v>10.62485447917098</v>
@@ -21052,7 +21052,7 @@
         <v>2.317255854164451</v>
       </c>
       <c r="D11" s="17" t="n">
-        <v>23.84440573497768</v>
+        <v>19.69745830324387</v>
       </c>
       <c r="E11" s="17" t="n"/>
       <c r="F11" s="17" t="n"/>
@@ -21068,7 +21068,7 @@
       </c>
       <c r="B12" s="17" t="n"/>
       <c r="C12" s="17" t="n">
-        <v>5.368803355554134</v>
+        <v>8.78035507207148</v>
       </c>
       <c r="D12" s="17" t="n">
         <v>-1.884904877076758</v>
@@ -21092,7 +21092,7 @@
         <v>-22.76854871668291</v>
       </c>
       <c r="F13" s="17" t="n">
-        <v>-26.68606553161489</v>
+        <v>-26.63159846685904</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>5</v>
@@ -21108,7 +21108,7 @@
         <v>122.4210371664149</v>
       </c>
       <c r="C14" s="17" t="n">
-        <v>148.4066559725991</v>
+        <v>11.970593811219</v>
       </c>
       <c r="D14" s="17" t="n"/>
       <c r="E14" s="17" t="n"/>
@@ -21148,7 +21148,7 @@
         <v>41.45047005974158</v>
       </c>
       <c r="C16" s="17" t="n">
-        <v>17.41923973136595</v>
+        <v>23.52648234417477</v>
       </c>
       <c r="D16" s="17" t="n"/>
       <c r="E16" s="17" t="n">
@@ -21166,7 +21166,7 @@
         </is>
       </c>
       <c r="B17" s="17" t="n">
-        <v>36.13415672797537</v>
+        <v>20.61068702290077</v>
       </c>
       <c r="C17" s="17" t="n"/>
       <c r="D17" s="17" t="n"/>
@@ -21187,7 +21187,7 @@
         <v>4.2185790251675</v>
       </c>
       <c r="D18" s="17" t="n">
-        <v>11.75767403602361</v>
+        <v>13.94048769341886</v>
       </c>
       <c r="E18" s="17" t="n"/>
       <c r="F18" s="17" t="n"/>
@@ -21198,7 +21198,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>Top 15 Customers — Overall Avg Variance %</t>
+          <t>Top 15 Customers — Overall Variance (Median leads; Mean shown for context)</t>
         </is>
       </c>
     </row>
@@ -21210,10 +21210,25 @@
       </c>
       <c r="B23" s="9" t="inlineStr">
         <is>
+          <t>Median Variance %</t>
+        </is>
+      </c>
+      <c r="C23" s="9" t="inlineStr">
+        <is>
           <t>Avg Variance %</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>Min %</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>Max %</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
         <is>
           <t>Quote Count</t>
         </is>
@@ -21226,9 +21241,18 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
+        <v>10.23090864341174</v>
+      </c>
+      <c r="C24" s="6" t="n">
         <v>13.72408282857755</v>
       </c>
-      <c r="C24" s="7" t="n">
+      <c r="D24" s="6" t="n">
+        <v>-46.99494062390221</v>
+      </c>
+      <c r="E24" s="6" t="n">
+        <v>73.88562484404419</v>
+      </c>
+      <c r="F24" s="7" t="n">
         <v>25</v>
       </c>
     </row>
@@ -21239,9 +21263,18 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
+        <v>13.71720216609844</v>
+      </c>
+      <c r="C25" s="6" t="n">
         <v>10.46580602207717</v>
       </c>
-      <c r="C25" s="7" t="n">
+      <c r="D25" s="6" t="n">
+        <v>-59.14340537681302</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>92.22150186041269</v>
+      </c>
+      <c r="F25" s="7" t="n">
         <v>21</v>
       </c>
     </row>
@@ -21252,9 +21285,18 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
+        <v>31.81931826577036</v>
+      </c>
+      <c r="C26" s="6" t="n">
         <v>35.40151033322152</v>
       </c>
-      <c r="C26" s="7" t="n">
+      <c r="D26" s="6" t="n">
+        <v>17.34705440011538</v>
+      </c>
+      <c r="E26" s="6" t="n">
+        <v>63.74144203500531</v>
+      </c>
+      <c r="F26" s="7" t="n">
         <v>14</v>
       </c>
     </row>
@@ -21265,9 +21307,18 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
+        <v>20.55470711715886</v>
+      </c>
+      <c r="C27" s="6" t="n">
         <v>24.11717047531249</v>
       </c>
-      <c r="C27" s="7" t="n">
+      <c r="D27" s="6" t="n">
+        <v>0.7048749911299275</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>81.31408646316598</v>
+      </c>
+      <c r="F27" s="7" t="n">
         <v>13</v>
       </c>
     </row>
@@ -21278,9 +21329,18 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
+        <v>20.62610713272247</v>
+      </c>
+      <c r="C28" s="6" t="n">
         <v>24.32457536914045</v>
       </c>
-      <c r="C28" s="7" t="n">
+      <c r="D28" s="6" t="n">
+        <v>8.108483683442572</v>
+      </c>
+      <c r="E28" s="6" t="n">
+        <v>56.92758476349936</v>
+      </c>
+      <c r="F28" s="7" t="n">
         <v>10</v>
       </c>
     </row>
@@ -21291,9 +21351,18 @@
         </is>
       </c>
       <c r="B29" s="6" t="n">
+        <v>0.8092089593470444</v>
+      </c>
+      <c r="C29" s="6" t="n">
         <v>22.66460872941541</v>
       </c>
-      <c r="C29" s="7" t="n">
+      <c r="D29" s="6" t="n">
+        <v>-22.52348631276127</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>197.6430278362778</v>
+      </c>
+      <c r="F29" s="7" t="n">
         <v>8</v>
       </c>
     </row>
@@ -21304,9 +21373,18 @@
         </is>
       </c>
       <c r="B30" s="6" t="n">
+        <v>26.79580696584707</v>
+      </c>
+      <c r="C30" s="6" t="n">
         <v>36.66245630866497</v>
       </c>
-      <c r="C30" s="7" t="n">
+      <c r="D30" s="6" t="n">
+        <v>4.750333173488505</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>96.05031412587979</v>
+      </c>
+      <c r="F30" s="7" t="n">
         <v>7</v>
       </c>
     </row>
@@ -21317,9 +21395,18 @@
         </is>
       </c>
       <c r="B31" s="6" t="n">
+        <v>17.1801596290104</v>
+      </c>
+      <c r="C31" s="6" t="n">
         <v>16.66868910803994</v>
       </c>
-      <c r="C31" s="7" t="n">
+      <c r="D31" s="6" t="n">
+        <v>-21.64239127255711</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>49.73094775474958</v>
+      </c>
+      <c r="F31" s="7" t="n">
         <v>6</v>
       </c>
     </row>
@@ -21330,9 +21417,18 @@
         </is>
       </c>
       <c r="B32" s="6" t="n">
+        <v>8.78035507207148</v>
+      </c>
+      <c r="C32" s="6" t="n">
         <v>2.467320062501777</v>
       </c>
-      <c r="C32" s="7" t="n">
+      <c r="D32" s="6" t="n">
+        <v>-15.48173445099866</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>11.85013327607052</v>
+      </c>
+      <c r="F32" s="7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -21343,9 +21439,18 @@
         </is>
       </c>
       <c r="B33" s="6" t="n">
+        <v>-26.05130320332367</v>
+      </c>
+      <c r="C33" s="6" t="n">
         <v>-25.1190588056421</v>
       </c>
-      <c r="C33" s="7" t="n">
+      <c r="D33" s="6" t="n">
+        <v>-27.37529492466198</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>-19.88996544608485</v>
+      </c>
+      <c r="F33" s="7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -21356,9 +21461,18 @@
         </is>
       </c>
       <c r="B34" s="6" t="n">
+        <v>31.28147072718262</v>
+      </c>
+      <c r="C34" s="6" t="n">
         <v>138.0124084501254</v>
       </c>
-      <c r="C34" s="7" t="n">
+      <c r="D34" s="6" t="n">
+        <v>-1.849589135645857</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>435.0989632422243</v>
+      </c>
+      <c r="F34" s="7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -21369,9 +21483,18 @@
         </is>
       </c>
       <c r="B35" s="6" t="n">
+        <v>26.38012480317256</v>
+      </c>
+      <c r="C35" s="6" t="n">
         <v>28.32270284958995</v>
       </c>
-      <c r="C35" s="7" t="n">
+      <c r="D35" s="6" t="n">
+        <v>-5.530480119787563</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>52.3679040430152</v>
+      </c>
+      <c r="F35" s="7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -21382,9 +21505,18 @@
         </is>
       </c>
       <c r="B36" s="6" t="n">
+        <v>23.52648234417477</v>
+      </c>
+      <c r="C36" s="6" t="n">
         <v>18.22122709822478</v>
       </c>
-      <c r="C36" s="7" t="n">
+      <c r="D36" s="6" t="n">
+        <v>-3.069886990991867</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>41.45047005974158</v>
+      </c>
+      <c r="F36" s="7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -21395,9 +21527,18 @@
         </is>
       </c>
       <c r="B37" s="6" t="n">
+        <v>20.61068702290077</v>
+      </c>
+      <c r="C37" s="6" t="n">
         <v>36.13415672797537</v>
       </c>
-      <c r="C37" s="7" t="n">
+      <c r="D37" s="6" t="n">
+        <v>9.498579130480984</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>97.43709504312915</v>
+      </c>
+      <c r="F37" s="7" t="n">
         <v>5</v>
       </c>
     </row>
@@ -21408,9 +21549,18 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
+        <v>9.611695030132362</v>
+      </c>
+      <c r="C38" s="6" t="n">
         <v>9.872900283309583</v>
       </c>
-      <c r="C38" s="7" t="n">
+      <c r="D38" s="6" t="n">
+        <v>4.2185790251675</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>16.04963204780611</v>
+      </c>
+      <c r="F38" s="7" t="n">
         <v>4</v>
       </c>
     </row>
